--- a/files/temp_files/statement_2025_10.xlsx
+++ b/files/temp_files/statement_2025_10.xlsx
@@ -597,7 +597,7 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>80.2</v>
+        <v>-80.2</v>
       </c>
       <c r="D2" t="s">
         <v>59</v>
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>62.51</v>
+        <v>-62.51</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -625,7 +625,7 @@
         <v>37</v>
       </c>
       <c r="C4">
-        <v>18.24</v>
+        <v>-18.24</v>
       </c>
       <c r="D4" t="s">
         <v>61</v>
@@ -639,7 +639,7 @@
         <v>38</v>
       </c>
       <c r="C5">
-        <v>97.90000000000001</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="D5" t="s">
         <v>59</v>
@@ -653,7 +653,7 @@
         <v>39</v>
       </c>
       <c r="C6">
-        <v>149.65</v>
+        <v>-149.65</v>
       </c>
       <c r="D6" t="s">
         <v>62</v>
@@ -667,7 +667,7 @@
         <v>38</v>
       </c>
       <c r="C7">
-        <v>101.69</v>
+        <v>-101.69</v>
       </c>
       <c r="D7" t="s">
         <v>59</v>
@@ -723,7 +723,7 @@
         <v>43</v>
       </c>
       <c r="C11">
-        <v>343.83</v>
+        <v>-343.83</v>
       </c>
       <c r="D11" t="s">
         <v>60</v>
@@ -737,7 +737,7 @@
         <v>44</v>
       </c>
       <c r="C12">
-        <v>105.24</v>
+        <v>-105.24</v>
       </c>
       <c r="D12" t="s">
         <v>59</v>
@@ -751,7 +751,7 @@
         <v>38</v>
       </c>
       <c r="C13">
-        <v>47</v>
+        <v>-47</v>
       </c>
       <c r="D13" t="s">
         <v>59</v>
@@ -779,7 +779,7 @@
         <v>45</v>
       </c>
       <c r="C15">
-        <v>156.92</v>
+        <v>-156.92</v>
       </c>
       <c r="D15" t="s">
         <v>62</v>
@@ -793,7 +793,7 @@
         <v>46</v>
       </c>
       <c r="C16">
-        <v>128.59</v>
+        <v>-128.59</v>
       </c>
       <c r="D16" t="s">
         <v>62</v>
@@ -807,7 +807,7 @@
         <v>36</v>
       </c>
       <c r="C17">
-        <v>148.85</v>
+        <v>-148.85</v>
       </c>
       <c r="D17" t="s">
         <v>60</v>
@@ -821,7 +821,7 @@
         <v>35</v>
       </c>
       <c r="C18">
-        <v>58.49</v>
+        <v>-58.49</v>
       </c>
       <c r="D18" t="s">
         <v>59</v>
@@ -835,7 +835,7 @@
         <v>47</v>
       </c>
       <c r="C19">
-        <v>5.02</v>
+        <v>-5.02</v>
       </c>
       <c r="D19" t="s">
         <v>64</v>
@@ -849,7 +849,7 @@
         <v>48</v>
       </c>
       <c r="C20">
-        <v>294.2</v>
+        <v>-294.2</v>
       </c>
       <c r="D20" t="s">
         <v>65</v>
@@ -877,7 +877,7 @@
         <v>47</v>
       </c>
       <c r="C22">
-        <v>21.69</v>
+        <v>-21.69</v>
       </c>
       <c r="D22" t="s">
         <v>64</v>
@@ -891,7 +891,7 @@
         <v>38</v>
       </c>
       <c r="C23">
-        <v>148.78</v>
+        <v>-148.78</v>
       </c>
       <c r="D23" t="s">
         <v>59</v>
@@ -905,7 +905,7 @@
         <v>48</v>
       </c>
       <c r="C24">
-        <v>246.91</v>
+        <v>-246.91</v>
       </c>
       <c r="D24" t="s">
         <v>65</v>
@@ -919,7 +919,7 @@
         <v>49</v>
       </c>
       <c r="C25">
-        <v>145.61</v>
+        <v>-145.61</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -947,7 +947,7 @@
         <v>50</v>
       </c>
       <c r="C27">
-        <v>204.06</v>
+        <v>-204.06</v>
       </c>
       <c r="D27" t="s">
         <v>65</v>
@@ -961,7 +961,7 @@
         <v>46</v>
       </c>
       <c r="C28">
-        <v>32.03</v>
+        <v>-32.03</v>
       </c>
       <c r="D28" t="s">
         <v>62</v>
@@ -975,7 +975,7 @@
         <v>51</v>
       </c>
       <c r="C29">
-        <v>403.89</v>
+        <v>-403.89</v>
       </c>
       <c r="D29" t="s">
         <v>66</v>
@@ -989,7 +989,7 @@
         <v>38</v>
       </c>
       <c r="C30">
-        <v>48.19</v>
+        <v>-48.19</v>
       </c>
       <c r="D30" t="s">
         <v>59</v>
@@ -1003,7 +1003,7 @@
         <v>37</v>
       </c>
       <c r="C31">
-        <v>42.65</v>
+        <v>-42.65</v>
       </c>
       <c r="D31" t="s">
         <v>61</v>
@@ -1031,7 +1031,7 @@
         <v>48</v>
       </c>
       <c r="C33">
-        <v>257.69</v>
+        <v>-257.69</v>
       </c>
       <c r="D33" t="s">
         <v>65</v>
@@ -1059,7 +1059,7 @@
         <v>44</v>
       </c>
       <c r="C35">
-        <v>110.17</v>
+        <v>-110.17</v>
       </c>
       <c r="D35" t="s">
         <v>59</v>
@@ -1073,7 +1073,7 @@
         <v>38</v>
       </c>
       <c r="C36">
-        <v>133.92</v>
+        <v>-133.92</v>
       </c>
       <c r="D36" t="s">
         <v>59</v>
@@ -1101,7 +1101,7 @@
         <v>52</v>
       </c>
       <c r="C38">
-        <v>93.98</v>
+        <v>-93.98</v>
       </c>
       <c r="D38" t="s">
         <v>61</v>
@@ -1115,7 +1115,7 @@
         <v>53</v>
       </c>
       <c r="C39">
-        <v>11.6</v>
+        <v>-11.6</v>
       </c>
       <c r="D39" t="s">
         <v>64</v>
@@ -1129,7 +1129,7 @@
         <v>54</v>
       </c>
       <c r="C40">
-        <v>6.12</v>
+        <v>-6.12</v>
       </c>
       <c r="D40" t="s">
         <v>64</v>
@@ -1143,7 +1143,7 @@
         <v>37</v>
       </c>
       <c r="C41">
-        <v>64.92</v>
+        <v>-64.92</v>
       </c>
       <c r="D41" t="s">
         <v>61</v>
@@ -1157,7 +1157,7 @@
         <v>55</v>
       </c>
       <c r="C42">
-        <v>723.98</v>
+        <v>-723.98</v>
       </c>
       <c r="D42" t="s">
         <v>66</v>
@@ -1171,7 +1171,7 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>166</v>
+        <v>-166</v>
       </c>
       <c r="D43" t="s">
         <v>65</v>
@@ -1185,7 +1185,7 @@
         <v>56</v>
       </c>
       <c r="C44">
-        <v>384.92</v>
+        <v>-384.92</v>
       </c>
       <c r="D44" t="s">
         <v>60</v>
@@ -1213,7 +1213,7 @@
         <v>50</v>
       </c>
       <c r="C46">
-        <v>89.86</v>
+        <v>-89.86</v>
       </c>
       <c r="D46" t="s">
         <v>65</v>
@@ -1227,7 +1227,7 @@
         <v>57</v>
       </c>
       <c r="C47">
-        <v>286.93</v>
+        <v>-286.93</v>
       </c>
       <c r="D47" t="s">
         <v>66</v>
@@ -1269,7 +1269,7 @@
         <v>46</v>
       </c>
       <c r="C50">
-        <v>40.05</v>
+        <v>-40.05</v>
       </c>
       <c r="D50" t="s">
         <v>62</v>
@@ -1283,7 +1283,7 @@
         <v>49</v>
       </c>
       <c r="C51">
-        <v>184.04</v>
+        <v>-184.04</v>
       </c>
       <c r="D51" t="s">
         <v>65</v>
@@ -1297,7 +1297,7 @@
         <v>50</v>
       </c>
       <c r="C52">
-        <v>58.58</v>
+        <v>-58.58</v>
       </c>
       <c r="D52" t="s">
         <v>65</v>
@@ -1311,7 +1311,7 @@
         <v>54</v>
       </c>
       <c r="C53">
-        <v>36.14</v>
+        <v>-36.14</v>
       </c>
       <c r="D53" t="s">
         <v>64</v>
@@ -1325,7 +1325,7 @@
         <v>54</v>
       </c>
       <c r="C54">
-        <v>24.46</v>
+        <v>-24.46</v>
       </c>
       <c r="D54" t="s">
         <v>64</v>
@@ -1339,7 +1339,7 @@
         <v>46</v>
       </c>
       <c r="C55">
-        <v>66.91</v>
+        <v>-66.91</v>
       </c>
       <c r="D55" t="s">
         <v>62</v>
@@ -1367,7 +1367,7 @@
         <v>47</v>
       </c>
       <c r="C57">
-        <v>12.25</v>
+        <v>-12.25</v>
       </c>
       <c r="D57" t="s">
         <v>64</v>
@@ -1381,7 +1381,7 @@
         <v>55</v>
       </c>
       <c r="C58">
-        <v>5.48</v>
+        <v>-5.48</v>
       </c>
       <c r="D58" t="s">
         <v>66</v>
@@ -1395,7 +1395,7 @@
         <v>53</v>
       </c>
       <c r="C59">
-        <v>23.61</v>
+        <v>-23.61</v>
       </c>
       <c r="D59" t="s">
         <v>64</v>
@@ -1409,7 +1409,7 @@
         <v>38</v>
       </c>
       <c r="C60">
-        <v>48.38</v>
+        <v>-48.38</v>
       </c>
       <c r="D60" t="s">
         <v>59</v>
@@ -1423,7 +1423,7 @@
         <v>46</v>
       </c>
       <c r="C61">
-        <v>145.14</v>
+        <v>-145.14</v>
       </c>
       <c r="D61" t="s">
         <v>62</v>
@@ -1437,7 +1437,7 @@
         <v>52</v>
       </c>
       <c r="C62">
-        <v>62.01</v>
+        <v>-62.01</v>
       </c>
       <c r="D62" t="s">
         <v>61</v>
@@ -1451,7 +1451,7 @@
         <v>54</v>
       </c>
       <c r="C63">
-        <v>36.87</v>
+        <v>-36.87</v>
       </c>
       <c r="D63" t="s">
         <v>64</v>
@@ -1479,7 +1479,7 @@
         <v>35</v>
       </c>
       <c r="C65">
-        <v>62.08</v>
+        <v>-62.08</v>
       </c>
       <c r="D65" t="s">
         <v>59</v>
@@ -1493,7 +1493,7 @@
         <v>37</v>
       </c>
       <c r="C66">
-        <v>48.81</v>
+        <v>-48.81</v>
       </c>
       <c r="D66" t="s">
         <v>61</v>
@@ -1507,7 +1507,7 @@
         <v>53</v>
       </c>
       <c r="C67">
-        <v>27.98</v>
+        <v>-27.98</v>
       </c>
       <c r="D67" t="s">
         <v>64</v>
@@ -1521,7 +1521,7 @@
         <v>45</v>
       </c>
       <c r="C68">
-        <v>190.81</v>
+        <v>-190.81</v>
       </c>
       <c r="D68" t="s">
         <v>62</v>
@@ -1535,7 +1535,7 @@
         <v>51</v>
       </c>
       <c r="C69">
-        <v>788.0700000000001</v>
+        <v>-788.0700000000001</v>
       </c>
       <c r="D69" t="s">
         <v>66</v>
@@ -1549,7 +1549,7 @@
         <v>49</v>
       </c>
       <c r="C70">
-        <v>157.92</v>
+        <v>-157.92</v>
       </c>
       <c r="D70" t="s">
         <v>65</v>
@@ -1563,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="C71">
-        <v>40.95</v>
+        <v>-40.95</v>
       </c>
       <c r="D71" t="s">
         <v>64</v>
@@ -1577,7 +1577,7 @@
         <v>38</v>
       </c>
       <c r="C72">
-        <v>45.72</v>
+        <v>-45.72</v>
       </c>
       <c r="D72" t="s">
         <v>59</v>
@@ -1591,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="C73">
-        <v>30.28</v>
+        <v>-30.28</v>
       </c>
       <c r="D73" t="s">
         <v>64</v>
@@ -1605,7 +1605,7 @@
         <v>55</v>
       </c>
       <c r="C74">
-        <v>462.97</v>
+        <v>-462.97</v>
       </c>
       <c r="D74" t="s">
         <v>66</v>
@@ -1619,7 +1619,7 @@
         <v>55</v>
       </c>
       <c r="C75">
-        <v>771.34</v>
+        <v>-771.34</v>
       </c>
       <c r="D75" t="s">
         <v>66</v>
@@ -1633,7 +1633,7 @@
         <v>52</v>
       </c>
       <c r="C76">
-        <v>98.81</v>
+        <v>-98.81</v>
       </c>
       <c r="D76" t="s">
         <v>61</v>
@@ -1647,7 +1647,7 @@
         <v>35</v>
       </c>
       <c r="C77">
-        <v>87.5</v>
+        <v>-87.5</v>
       </c>
       <c r="D77" t="s">
         <v>59</v>
@@ -1661,7 +1661,7 @@
         <v>39</v>
       </c>
       <c r="C78">
-        <v>27.84</v>
+        <v>-27.84</v>
       </c>
       <c r="D78" t="s">
         <v>62</v>
@@ -1675,7 +1675,7 @@
         <v>36</v>
       </c>
       <c r="C79">
-        <v>61.92</v>
+        <v>-61.92</v>
       </c>
       <c r="D79" t="s">
         <v>60</v>
@@ -1689,7 +1689,7 @@
         <v>54</v>
       </c>
       <c r="C80">
-        <v>8.99</v>
+        <v>-8.99</v>
       </c>
       <c r="D80" t="s">
         <v>64</v>
@@ -1703,7 +1703,7 @@
         <v>38</v>
       </c>
       <c r="C81">
-        <v>132.69</v>
+        <v>-132.69</v>
       </c>
       <c r="D81" t="s">
         <v>59</v>
@@ -1717,7 +1717,7 @@
         <v>49</v>
       </c>
       <c r="C82">
-        <v>290.28</v>
+        <v>-290.28</v>
       </c>
       <c r="D82" t="s">
         <v>65</v>
@@ -1731,7 +1731,7 @@
         <v>55</v>
       </c>
       <c r="C83">
-        <v>984.38</v>
+        <v>-984.38</v>
       </c>
       <c r="D83" t="s">
         <v>66</v>
@@ -1745,7 +1745,7 @@
         <v>47</v>
       </c>
       <c r="C84">
-        <v>38.41</v>
+        <v>-38.41</v>
       </c>
       <c r="D84" t="s">
         <v>64</v>
@@ -1759,7 +1759,7 @@
         <v>50</v>
       </c>
       <c r="C85">
-        <v>107.48</v>
+        <v>-107.48</v>
       </c>
       <c r="D85" t="s">
         <v>65</v>
@@ -1815,7 +1815,7 @@
         <v>43</v>
       </c>
       <c r="C89">
-        <v>8.9</v>
+        <v>-8.9</v>
       </c>
       <c r="D89" t="s">
         <v>60</v>
@@ -1829,7 +1829,7 @@
         <v>49</v>
       </c>
       <c r="C90">
-        <v>202.58</v>
+        <v>-202.58</v>
       </c>
       <c r="D90" t="s">
         <v>65</v>
@@ -1843,7 +1843,7 @@
         <v>38</v>
       </c>
       <c r="C91">
-        <v>116.51</v>
+        <v>-116.51</v>
       </c>
       <c r="D91" t="s">
         <v>59</v>
@@ -1857,7 +1857,7 @@
         <v>49</v>
       </c>
       <c r="C92">
-        <v>61.13</v>
+        <v>-61.13</v>
       </c>
       <c r="D92" t="s">
         <v>65</v>
@@ -1871,7 +1871,7 @@
         <v>55</v>
       </c>
       <c r="C93">
-        <v>259.26</v>
+        <v>-259.26</v>
       </c>
       <c r="D93" t="s">
         <v>66</v>
@@ -1885,7 +1885,7 @@
         <v>58</v>
       </c>
       <c r="C94">
-        <v>53.56</v>
+        <v>-53.56</v>
       </c>
       <c r="D94" t="s">
         <v>61</v>
@@ -1899,7 +1899,7 @@
         <v>54</v>
       </c>
       <c r="C95">
-        <v>39.45</v>
+        <v>-39.45</v>
       </c>
       <c r="D95" t="s">
         <v>64</v>
@@ -1913,7 +1913,7 @@
         <v>36</v>
       </c>
       <c r="C96">
-        <v>334.12</v>
+        <v>-334.12</v>
       </c>
       <c r="D96" t="s">
         <v>60</v>
@@ -1941,7 +1941,7 @@
         <v>53</v>
       </c>
       <c r="C98">
-        <v>48.82</v>
+        <v>-48.82</v>
       </c>
       <c r="D98" t="s">
         <v>64</v>
@@ -1955,7 +1955,7 @@
         <v>35</v>
       </c>
       <c r="C99">
-        <v>124.69</v>
+        <v>-124.69</v>
       </c>
       <c r="D99" t="s">
         <v>59</v>
@@ -1969,7 +1969,7 @@
         <v>53</v>
       </c>
       <c r="C100">
-        <v>42.54</v>
+        <v>-42.54</v>
       </c>
       <c r="D100" t="s">
         <v>64</v>
@@ -1983,7 +1983,7 @@
         <v>48</v>
       </c>
       <c r="C101">
-        <v>225.92</v>
+        <v>-225.92</v>
       </c>
       <c r="D101" t="s">
         <v>65</v>
@@ -1997,7 +1997,7 @@
         <v>46</v>
       </c>
       <c r="C102">
-        <v>183.37</v>
+        <v>-183.37</v>
       </c>
       <c r="D102" t="s">
         <v>62</v>
@@ -2011,7 +2011,7 @@
         <v>43</v>
       </c>
       <c r="C103">
-        <v>80.75</v>
+        <v>-80.75</v>
       </c>
       <c r="D103" t="s">
         <v>60</v>
@@ -2025,7 +2025,7 @@
         <v>55</v>
       </c>
       <c r="C104">
-        <v>817.14</v>
+        <v>-817.14</v>
       </c>
       <c r="D104" t="s">
         <v>66</v>
@@ -2039,7 +2039,7 @@
         <v>51</v>
       </c>
       <c r="C105">
-        <v>844.85</v>
+        <v>-844.85</v>
       </c>
       <c r="D105" t="s">
         <v>66</v>
@@ -2053,7 +2053,7 @@
         <v>46</v>
       </c>
       <c r="C106">
-        <v>19.29</v>
+        <v>-19.29</v>
       </c>
       <c r="D106" t="s">
         <v>62</v>
@@ -2067,7 +2067,7 @@
         <v>55</v>
       </c>
       <c r="C107">
-        <v>832.46</v>
+        <v>-832.46</v>
       </c>
       <c r="D107" t="s">
         <v>66</v>
@@ -2081,7 +2081,7 @@
         <v>49</v>
       </c>
       <c r="C108">
-        <v>227.73</v>
+        <v>-227.73</v>
       </c>
       <c r="D108" t="s">
         <v>65</v>
@@ -2095,7 +2095,7 @@
         <v>58</v>
       </c>
       <c r="C109">
-        <v>68.11</v>
+        <v>-68.11</v>
       </c>
       <c r="D109" t="s">
         <v>61</v>
@@ -2137,7 +2137,7 @@
         <v>43</v>
       </c>
       <c r="C112">
-        <v>482.59</v>
+        <v>-482.59</v>
       </c>
       <c r="D112" t="s">
         <v>60</v>
@@ -2151,7 +2151,7 @@
         <v>46</v>
       </c>
       <c r="C113">
-        <v>122.25</v>
+        <v>-122.25</v>
       </c>
       <c r="D113" t="s">
         <v>62</v>
@@ -2165,7 +2165,7 @@
         <v>36</v>
       </c>
       <c r="C114">
-        <v>81</v>
+        <v>-81</v>
       </c>
       <c r="D114" t="s">
         <v>60</v>
@@ -2179,7 +2179,7 @@
         <v>52</v>
       </c>
       <c r="C115">
-        <v>98.11</v>
+        <v>-98.11</v>
       </c>
       <c r="D115" t="s">
         <v>61</v>
@@ -2193,7 +2193,7 @@
         <v>44</v>
       </c>
       <c r="C116">
-        <v>89.55</v>
+        <v>-89.55</v>
       </c>
       <c r="D116" t="s">
         <v>59</v>
@@ -2207,7 +2207,7 @@
         <v>36</v>
       </c>
       <c r="C117">
-        <v>198.91</v>
+        <v>-198.91</v>
       </c>
       <c r="D117" t="s">
         <v>60</v>
@@ -2221,7 +2221,7 @@
         <v>56</v>
       </c>
       <c r="C118">
-        <v>207.18</v>
+        <v>-207.18</v>
       </c>
       <c r="D118" t="s">
         <v>60</v>
@@ -2235,7 +2235,7 @@
         <v>51</v>
       </c>
       <c r="C119">
-        <v>816.05</v>
+        <v>-816.05</v>
       </c>
       <c r="D119" t="s">
         <v>66</v>
@@ -2249,7 +2249,7 @@
         <v>35</v>
       </c>
       <c r="C120">
-        <v>41.73</v>
+        <v>-41.73</v>
       </c>
       <c r="D120" t="s">
         <v>59</v>
@@ -2263,7 +2263,7 @@
         <v>35</v>
       </c>
       <c r="C121">
-        <v>87.36</v>
+        <v>-87.36</v>
       </c>
       <c r="D121" t="s">
         <v>59</v>
@@ -2277,7 +2277,7 @@
         <v>37</v>
       </c>
       <c r="C122">
-        <v>79.42</v>
+        <v>-79.42</v>
       </c>
       <c r="D122" t="s">
         <v>61</v>
@@ -2291,7 +2291,7 @@
         <v>58</v>
       </c>
       <c r="C123">
-        <v>33.86</v>
+        <v>-33.86</v>
       </c>
       <c r="D123" t="s">
         <v>61</v>
@@ -2319,7 +2319,7 @@
         <v>49</v>
       </c>
       <c r="C125">
-        <v>259.59</v>
+        <v>-259.59</v>
       </c>
       <c r="D125" t="s">
         <v>65</v>
@@ -2333,7 +2333,7 @@
         <v>35</v>
       </c>
       <c r="C126">
-        <v>95.26000000000001</v>
+        <v>-95.26000000000001</v>
       </c>
       <c r="D126" t="s">
         <v>59</v>
@@ -2347,7 +2347,7 @@
         <v>35</v>
       </c>
       <c r="C127">
-        <v>62.31</v>
+        <v>-62.31</v>
       </c>
       <c r="D127" t="s">
         <v>59</v>
@@ -2375,7 +2375,7 @@
         <v>47</v>
       </c>
       <c r="C129">
-        <v>31.19</v>
+        <v>-31.19</v>
       </c>
       <c r="D129" t="s">
         <v>64</v>
@@ -2417,7 +2417,7 @@
         <v>53</v>
       </c>
       <c r="C132">
-        <v>12.84</v>
+        <v>-12.84</v>
       </c>
       <c r="D132" t="s">
         <v>64</v>
@@ -2431,7 +2431,7 @@
         <v>46</v>
       </c>
       <c r="C133">
-        <v>108.31</v>
+        <v>-108.31</v>
       </c>
       <c r="D133" t="s">
         <v>62</v>
@@ -2445,7 +2445,7 @@
         <v>49</v>
       </c>
       <c r="C134">
-        <v>205.51</v>
+        <v>-205.51</v>
       </c>
       <c r="D134" t="s">
         <v>65</v>
@@ -2473,7 +2473,7 @@
         <v>53</v>
       </c>
       <c r="C136">
-        <v>25.19</v>
+        <v>-25.19</v>
       </c>
       <c r="D136" t="s">
         <v>64</v>
@@ -2487,7 +2487,7 @@
         <v>38</v>
       </c>
       <c r="C137">
-        <v>24.5</v>
+        <v>-24.5</v>
       </c>
       <c r="D137" t="s">
         <v>59</v>
@@ -2501,7 +2501,7 @@
         <v>54</v>
       </c>
       <c r="C138">
-        <v>30.96</v>
+        <v>-30.96</v>
       </c>
       <c r="D138" t="s">
         <v>64</v>
@@ -2515,7 +2515,7 @@
         <v>55</v>
       </c>
       <c r="C139">
-        <v>9.17</v>
+        <v>-9.17</v>
       </c>
       <c r="D139" t="s">
         <v>66</v>
@@ -2529,7 +2529,7 @@
         <v>51</v>
       </c>
       <c r="C140">
-        <v>726.86</v>
+        <v>-726.86</v>
       </c>
       <c r="D140" t="s">
         <v>66</v>
@@ -2543,7 +2543,7 @@
         <v>51</v>
       </c>
       <c r="C141">
-        <v>523.41</v>
+        <v>-523.41</v>
       </c>
       <c r="D141" t="s">
         <v>66</v>
@@ -2557,7 +2557,7 @@
         <v>53</v>
       </c>
       <c r="C142">
-        <v>35.44</v>
+        <v>-35.44</v>
       </c>
       <c r="D142" t="s">
         <v>64</v>
@@ -2571,7 +2571,7 @@
         <v>54</v>
       </c>
       <c r="C143">
-        <v>45.14</v>
+        <v>-45.14</v>
       </c>
       <c r="D143" t="s">
         <v>64</v>
@@ -2585,7 +2585,7 @@
         <v>43</v>
       </c>
       <c r="C144">
-        <v>47.13</v>
+        <v>-47.13</v>
       </c>
       <c r="D144" t="s">
         <v>60</v>
@@ -2599,7 +2599,7 @@
         <v>55</v>
       </c>
       <c r="C145">
-        <v>221.56</v>
+        <v>-221.56</v>
       </c>
       <c r="D145" t="s">
         <v>66</v>
@@ -2613,7 +2613,7 @@
         <v>35</v>
       </c>
       <c r="C146">
-        <v>136.13</v>
+        <v>-136.13</v>
       </c>
       <c r="D146" t="s">
         <v>59</v>
@@ -2641,7 +2641,7 @@
         <v>57</v>
       </c>
       <c r="C148">
-        <v>667.71</v>
+        <v>-667.71</v>
       </c>
       <c r="D148" t="s">
         <v>66</v>
@@ -2655,7 +2655,7 @@
         <v>54</v>
       </c>
       <c r="C149">
-        <v>1.13</v>
+        <v>-1.13</v>
       </c>
       <c r="D149" t="s">
         <v>64</v>
@@ -2669,7 +2669,7 @@
         <v>43</v>
       </c>
       <c r="C150">
-        <v>88.34</v>
+        <v>-88.34</v>
       </c>
       <c r="D150" t="s">
         <v>60</v>
@@ -2683,7 +2683,7 @@
         <v>47</v>
       </c>
       <c r="C151">
-        <v>19.79</v>
+        <v>-19.79</v>
       </c>
       <c r="D151" t="s">
         <v>64</v>
@@ -2697,7 +2697,7 @@
         <v>37</v>
       </c>
       <c r="C152">
-        <v>48.3</v>
+        <v>-48.3</v>
       </c>
       <c r="D152" t="s">
         <v>61</v>
@@ -2711,7 +2711,7 @@
         <v>43</v>
       </c>
       <c r="C153">
-        <v>176.86</v>
+        <v>-176.86</v>
       </c>
       <c r="D153" t="s">
         <v>60</v>
@@ -2725,7 +2725,7 @@
         <v>47</v>
       </c>
       <c r="C154">
-        <v>21.37</v>
+        <v>-21.37</v>
       </c>
       <c r="D154" t="s">
         <v>64</v>
@@ -2739,7 +2739,7 @@
         <v>47</v>
       </c>
       <c r="C155">
-        <v>23.45</v>
+        <v>-23.45</v>
       </c>
       <c r="D155" t="s">
         <v>64</v>
@@ -2753,7 +2753,7 @@
         <v>36</v>
       </c>
       <c r="C156">
-        <v>291.51</v>
+        <v>-291.51</v>
       </c>
       <c r="D156" t="s">
         <v>60</v>
@@ -2767,7 +2767,7 @@
         <v>45</v>
       </c>
       <c r="C157">
-        <v>135.89</v>
+        <v>-135.89</v>
       </c>
       <c r="D157" t="s">
         <v>62</v>
@@ -2781,7 +2781,7 @@
         <v>56</v>
       </c>
       <c r="C158">
-        <v>107.26</v>
+        <v>-107.26</v>
       </c>
       <c r="D158" t="s">
         <v>60</v>
@@ -2809,7 +2809,7 @@
         <v>39</v>
       </c>
       <c r="C160">
-        <v>186.29</v>
+        <v>-186.29</v>
       </c>
       <c r="D160" t="s">
         <v>62</v>
@@ -2823,7 +2823,7 @@
         <v>57</v>
       </c>
       <c r="C161">
-        <v>177.74</v>
+        <v>-177.74</v>
       </c>
       <c r="D161" t="s">
         <v>66</v>
@@ -2837,7 +2837,7 @@
         <v>44</v>
       </c>
       <c r="C162">
-        <v>21.54</v>
+        <v>-21.54</v>
       </c>
       <c r="D162" t="s">
         <v>59</v>
@@ -2851,7 +2851,7 @@
         <v>56</v>
       </c>
       <c r="C163">
-        <v>339.35</v>
+        <v>-339.35</v>
       </c>
       <c r="D163" t="s">
         <v>60</v>
@@ -2865,7 +2865,7 @@
         <v>55</v>
       </c>
       <c r="C164">
-        <v>34.42</v>
+        <v>-34.42</v>
       </c>
       <c r="D164" t="s">
         <v>66</v>
@@ -2879,7 +2879,7 @@
         <v>38</v>
       </c>
       <c r="C165">
-        <v>91.73</v>
+        <v>-91.73</v>
       </c>
       <c r="D165" t="s">
         <v>59</v>
@@ -2893,7 +2893,7 @@
         <v>50</v>
       </c>
       <c r="C166">
-        <v>94.14</v>
+        <v>-94.14</v>
       </c>
       <c r="D166" t="s">
         <v>65</v>
@@ -2907,7 +2907,7 @@
         <v>37</v>
       </c>
       <c r="C167">
-        <v>89.11</v>
+        <v>-89.11</v>
       </c>
       <c r="D167" t="s">
         <v>61</v>
@@ -2921,7 +2921,7 @@
         <v>43</v>
       </c>
       <c r="C168">
-        <v>54.24</v>
+        <v>-54.24</v>
       </c>
       <c r="D168" t="s">
         <v>60</v>
@@ -2935,7 +2935,7 @@
         <v>48</v>
       </c>
       <c r="C169">
-        <v>87.31</v>
+        <v>-87.31</v>
       </c>
       <c r="D169" t="s">
         <v>65</v>
@@ -2949,7 +2949,7 @@
         <v>36</v>
       </c>
       <c r="C170">
-        <v>311.83</v>
+        <v>-311.83</v>
       </c>
       <c r="D170" t="s">
         <v>60</v>
@@ -2963,7 +2963,7 @@
         <v>44</v>
       </c>
       <c r="C171">
-        <v>136.16</v>
+        <v>-136.16</v>
       </c>
       <c r="D171" t="s">
         <v>59</v>
@@ -2977,7 +2977,7 @@
         <v>37</v>
       </c>
       <c r="C172">
-        <v>77.22</v>
+        <v>-77.22</v>
       </c>
       <c r="D172" t="s">
         <v>61</v>
@@ -2991,7 +2991,7 @@
         <v>37</v>
       </c>
       <c r="C173">
-        <v>60.79</v>
+        <v>-60.79</v>
       </c>
       <c r="D173" t="s">
         <v>61</v>
@@ -3005,7 +3005,7 @@
         <v>57</v>
       </c>
       <c r="C174">
-        <v>961</v>
+        <v>-961</v>
       </c>
       <c r="D174" t="s">
         <v>66</v>
@@ -3019,7 +3019,7 @@
         <v>46</v>
       </c>
       <c r="C175">
-        <v>134.99</v>
+        <v>-134.99</v>
       </c>
       <c r="D175" t="s">
         <v>62</v>
@@ -3033,7 +3033,7 @@
         <v>51</v>
       </c>
       <c r="C176">
-        <v>566.92</v>
+        <v>-566.92</v>
       </c>
       <c r="D176" t="s">
         <v>66</v>
@@ -3061,7 +3061,7 @@
         <v>53</v>
       </c>
       <c r="C178">
-        <v>46.32</v>
+        <v>-46.32</v>
       </c>
       <c r="D178" t="s">
         <v>64</v>
@@ -3075,7 +3075,7 @@
         <v>56</v>
       </c>
       <c r="C179">
-        <v>293.96</v>
+        <v>-293.96</v>
       </c>
       <c r="D179" t="s">
         <v>60</v>
@@ -3089,7 +3089,7 @@
         <v>50</v>
       </c>
       <c r="C180">
-        <v>170.34</v>
+        <v>-170.34</v>
       </c>
       <c r="D180" t="s">
         <v>65</v>
@@ -3103,7 +3103,7 @@
         <v>50</v>
       </c>
       <c r="C181">
-        <v>261</v>
+        <v>-261</v>
       </c>
       <c r="D181" t="s">
         <v>65</v>
@@ -3131,7 +3131,7 @@
         <v>43</v>
       </c>
       <c r="C183">
-        <v>78.45</v>
+        <v>-78.45</v>
       </c>
       <c r="D183" t="s">
         <v>60</v>
@@ -3145,7 +3145,7 @@
         <v>45</v>
       </c>
       <c r="C184">
-        <v>140.16</v>
+        <v>-140.16</v>
       </c>
       <c r="D184" t="s">
         <v>62</v>
@@ -3159,7 +3159,7 @@
         <v>49</v>
       </c>
       <c r="C185">
-        <v>232.52</v>
+        <v>-232.52</v>
       </c>
       <c r="D185" t="s">
         <v>65</v>
@@ -3173,7 +3173,7 @@
         <v>35</v>
       </c>
       <c r="C186">
-        <v>116.33</v>
+        <v>-116.33</v>
       </c>
       <c r="D186" t="s">
         <v>59</v>
@@ -3187,7 +3187,7 @@
         <v>44</v>
       </c>
       <c r="C187">
-        <v>87.40000000000001</v>
+        <v>-87.40000000000001</v>
       </c>
       <c r="D187" t="s">
         <v>59</v>
@@ -3215,7 +3215,7 @@
         <v>35</v>
       </c>
       <c r="C189">
-        <v>135.67</v>
+        <v>-135.67</v>
       </c>
       <c r="D189" t="s">
         <v>59</v>
@@ -3229,7 +3229,7 @@
         <v>49</v>
       </c>
       <c r="C190">
-        <v>141.37</v>
+        <v>-141.37</v>
       </c>
       <c r="D190" t="s">
         <v>65</v>
@@ -3243,7 +3243,7 @@
         <v>52</v>
       </c>
       <c r="C191">
-        <v>21.01</v>
+        <v>-21.01</v>
       </c>
       <c r="D191" t="s">
         <v>61</v>
@@ -3257,7 +3257,7 @@
         <v>57</v>
       </c>
       <c r="C192">
-        <v>373.72</v>
+        <v>-373.72</v>
       </c>
       <c r="D192" t="s">
         <v>66</v>
@@ -3271,7 +3271,7 @@
         <v>43</v>
       </c>
       <c r="C193">
-        <v>414.22</v>
+        <v>-414.22</v>
       </c>
       <c r="D193" t="s">
         <v>60</v>
@@ -3285,7 +3285,7 @@
         <v>58</v>
       </c>
       <c r="C194">
-        <v>15.03</v>
+        <v>-15.03</v>
       </c>
       <c r="D194" t="s">
         <v>61</v>
@@ -3299,7 +3299,7 @@
         <v>56</v>
       </c>
       <c r="C195">
-        <v>426.93</v>
+        <v>-426.93</v>
       </c>
       <c r="D195" t="s">
         <v>60</v>
@@ -3313,7 +3313,7 @@
         <v>37</v>
       </c>
       <c r="C196">
-        <v>68.98999999999999</v>
+        <v>-68.98999999999999</v>
       </c>
       <c r="D196" t="s">
         <v>61</v>
@@ -3341,7 +3341,7 @@
         <v>50</v>
       </c>
       <c r="C198">
-        <v>183.86</v>
+        <v>-183.86</v>
       </c>
       <c r="D198" t="s">
         <v>65</v>
@@ -3369,7 +3369,7 @@
         <v>53</v>
       </c>
       <c r="C200">
-        <v>27.48</v>
+        <v>-27.48</v>
       </c>
       <c r="D200" t="s">
         <v>64</v>
@@ -3383,7 +3383,7 @@
         <v>58</v>
       </c>
       <c r="C201">
-        <v>95.48</v>
+        <v>-95.48</v>
       </c>
       <c r="D201" t="s">
         <v>61</v>
